--- a/real_estate_forms/002_property_information_form--real_estate_forms.xlsx
+++ b/real_estate_forms/002_property_information_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{0:_'alabama'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{0: 'Alabama'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{1:_'alaska'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{1: 'Alaska'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{2:_'american_samoa'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{2: 'American Samoa'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{3:_'arizona'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{3: 'Arizona'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{4:_'arkansas'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{4: 'Arkansas'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{5:_'armed_forces_-_hawaii'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{5: 'Armed Forces - Hawaii'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{6:_'armed_forces_-_washington_dc'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{6: 'Armed Forces - Washington DC'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{7:_'california'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{7: 'California'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{8:_'colorado'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{8: 'Colorado'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{9:_'connecticut'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{9: 'Connecticut'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{10:_'delaware'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{10: 'Delaware'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{11:_'district_of_columbia'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{11: 'District of Columbia'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{12:_'florida'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{12: 'Florida'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{13:_'georgia'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{13: 'Georgia'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{14:_'guam'}</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{14: 'Guam'}</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{15:_'hawaii'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{15: 'Hawaii'}</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{16:_'idaho'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{16: 'Idaho'}</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{17:_'illinois'}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{17: 'Illinois'}</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{18:_'indiana'}</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{18: 'Indiana'}</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{19:_'iowa'}</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{19: 'Iowa'}</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{20:_'kansas'}</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{20: 'Kansas'}</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{21:_'kentucky'}</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{21: 'Kentucky'}</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{22:_'louisiana'}</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{22: 'Louisiana'}</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{23:_'maine'}</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{23: 'Maine'}</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{24:_'maryland'}</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{24: 'Maryland'}</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{25:_'massachusetts'}</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{25: 'Massachusetts'}</t>
+          <t>Option 26</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{26:_'michigan'}</t>
+          <t>option_27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{26: 'Michigan'}</t>
+          <t>Option 27</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{27:_'minnesota'}</t>
+          <t>option_28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{27: 'Minnesota'}</t>
+          <t>Option 28</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{28:_'mississippi'}</t>
+          <t>option_29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{28: 'Mississippi'}</t>
+          <t>Option 29</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{29:_'missouri'}</t>
+          <t>option_30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{29: 'Missouri'}</t>
+          <t>Option 30</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{30:_'montana'}</t>
+          <t>option_31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{30: 'Montana'}</t>
+          <t>Option 31</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{31:_'nebraska'}</t>
+          <t>option_32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{31: 'Nebraska'}</t>
+          <t>Option 32</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{32:_'nevada'}</t>
+          <t>option_33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{32: 'Nevada'}</t>
+          <t>Option 33</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{33:_'new_hampshire'}</t>
+          <t>option_34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{33: 'New Hampshire'}</t>
+          <t>Option 34</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{34:_'new_jersey'}</t>
+          <t>option_35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{34: 'New Jersey'}</t>
+          <t>Option 35</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{35:_'new_mexico'}</t>
+          <t>option_36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{35: 'New Mexico'}</t>
+          <t>Option 36</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{36:_'new_york'}</t>
+          <t>option_37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{36: 'New York'}</t>
+          <t>Option 37</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{37:_'north_carolina'}</t>
+          <t>option_38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{37: 'North Carolina'}</t>
+          <t>Option 38</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{38:_'north_dakota'}</t>
+          <t>option_39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{38: 'North Dakota'}</t>
+          <t>Option 39</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{39:_'northern_mariana_islands'}</t>
+          <t>option_40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{39: 'Northern Mariana Islands'}</t>
+          <t>Option 40</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{40:_'ohio'}</t>
+          <t>option_41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{40: 'Ohio'}</t>
+          <t>Option 41</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{41:_'oklahoma'}</t>
+          <t>option_42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{41: 'Oklahoma'}</t>
+          <t>Option 42</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{42:_'oregon'}</t>
+          <t>option_43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{42: 'Oregon'}</t>
+          <t>Option 43</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{43:_'pennsylvania'}</t>
+          <t>option_44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{43: 'Pennsylvania'}</t>
+          <t>Option 44</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{44:_'puerto_rico'}</t>
+          <t>option_45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{44: 'Puerto Rico'}</t>
+          <t>Option 45</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{45:_'rhode_island'}</t>
+          <t>option_46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{45: 'Rhode Island'}</t>
+          <t>Option 46</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{46:_'south_carolina'}</t>
+          <t>option_47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{46: 'South Carolina'}</t>
+          <t>Option 47</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{47:_'south_dakota'}</t>
+          <t>option_48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{47: 'South Dakota'}</t>
+          <t>Option 48</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{48:_'tennessee'}</t>
+          <t>option_49</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{48: 'Tennessee'}</t>
+          <t>Option 49</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{49:_'texas'}</t>
+          <t>option_50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{49: 'Texas'}</t>
+          <t>Option 50</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{50:_'utah'}</t>
+          <t>option_51</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{50: 'Utah'}</t>
+          <t>Option 51</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{51:_'vermont'}</t>
+          <t>option_52</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{51: 'Vermont'}</t>
+          <t>Option 52</t>
         </is>
       </c>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{52:_'virgin_islands'}</t>
+          <t>option_53</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{52: 'Virgin Islands'}</t>
+          <t>Option 53</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{53:_'virginia'}</t>
+          <t>option_54</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{53: 'Virginia'}</t>
+          <t>Option 54</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{54:_'washington'}</t>
+          <t>option_55</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{54: 'Washington'}</t>
+          <t>Option 55</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{55:_'washington_dc'}</t>
+          <t>option_56</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{55: 'Washington DC'}</t>
+          <t>Option 56</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{56:_'west_virginia'}</t>
+          <t>option_57</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{56: 'West Virginia'}</t>
+          <t>Option 57</t>
         </is>
       </c>
     </row>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{57:_'wisconsin'}</t>
+          <t>option_58</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{57: 'Wisconsin'}</t>
+          <t>Option 58</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{58:_'wyoming'}</t>
+          <t>option_59</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{58: 'Wyoming'}</t>
+          <t>Option 59</t>
         </is>
       </c>
     </row>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{0:_'condo'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{0: 'Condo'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{1:_'townhouse'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{1: 'Townhouse'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{2:_'single_family_home'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{2: 'Single Family Home'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{3:_'apartment'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{3: 'Apartment'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{4:_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{4: 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{0:_'new'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{0: 'New'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{1:_'used'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{1: 'Used'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2184,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{2:_'other'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{2: 'Other'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{0:_'active'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{0: 'Active'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{1:_'sold'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{1: 'Sold'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2235,12 +2235,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{2:_'leased'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{2: 'Leased'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{3:_'inactive'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{3: 'Inactive'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{0:_'real_estate_agent_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{0: 'Real Estate Agent 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{1:_'real_estate_agent_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{1: 'Real Estate Agent 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{2:_'real_estate_agent_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{2: 'Real Estate Agent 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{3:_'other'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{3: 'Other'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
